--- a/artfynd/A 15925-2026 artfynd.xlsx
+++ b/artfynd/A 15925-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -908,6 +908,1452 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>132830899</v>
+      </c>
+      <c r="B4" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Skarnbro, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>696275</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6643599</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>132827217</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ramaren, Ramaren, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>696300</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6643713</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>132827269</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ramaren, Ramaren, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>696289</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6643668</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>132830905</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ramaren, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>696297</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6643754</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>132827060</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ramaren, Ramaren, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>696289</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6643730</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>132830909</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Skarnbro, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>696293</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6643676</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>132830900</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Skarnbro, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>696261</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6643641</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>132827302</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ramaren, Ramaren, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>696294</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6643666</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>132830903</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Skarnbro, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>696214</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6643713</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>132830907</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Skarnbro, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>696302</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6643711</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>132830908</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Skarnbro, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>696294</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6643676</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>132830904</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Skarnbro, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>696201</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6643715</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>132827400</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ramaren, Ramaren, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>696298</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6643648</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 15925-2026 artfynd.xlsx
+++ b/artfynd/A 15925-2026 artfynd.xlsx
@@ -910,45 +910,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132830899</v>
+        <v>132827217</v>
       </c>
       <c r="B4" t="n">
-        <v>101326</v>
+        <v>91910</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skarnbro, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>696275</v>
+        <v>696300</v>
       </c>
       <c r="R4" t="n">
-        <v>6643599</v>
+        <v>6643713</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,57 +1005,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132827217</v>
+        <v>132830899</v>
       </c>
       <c r="B5" t="n">
-        <v>91909</v>
+        <v>101327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Skarnbro, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>696300</v>
+        <v>696275</v>
       </c>
       <c r="R5" t="n">
-        <v>6643713</v>
+        <v>6643599</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,12 +1112,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1127,7 +1127,7 @@
         <v>132827269</v>
       </c>
       <c r="B6" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>132830905</v>
       </c>
       <c r="B7" t="n">
-        <v>101326</v>
+        <v>101327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>132827060</v>
       </c>
       <c r="B8" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1462,7 +1462,7 @@
         <v>132830909</v>
       </c>
       <c r="B9" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>132830900</v>
       </c>
       <c r="B10" t="n">
-        <v>101326</v>
+        <v>101327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>132827302</v>
       </c>
       <c r="B11" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,54 +1794,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132830903</v>
+        <v>132830907</v>
       </c>
       <c r="B12" t="n">
-        <v>99118</v>
+        <v>91910</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skarnbro, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>696214</v>
+        <v>696302</v>
       </c>
       <c r="R12" t="n">
-        <v>6643713</v>
+        <v>6643711</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1873,7 +1864,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1883,7 +1874,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1910,45 +1901,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132830907</v>
+        <v>132830903</v>
       </c>
       <c r="B13" t="n">
-        <v>91909</v>
+        <v>99119</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skarnbro, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>696302</v>
+        <v>696214</v>
       </c>
       <c r="R13" t="n">
-        <v>6643711</v>
+        <v>6643713</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2020,7 +2020,7 @@
         <v>132830908</v>
       </c>
       <c r="B14" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>132830904</v>
       </c>
       <c r="B15" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>132827400</v>
       </c>
       <c r="B16" t="n">
-        <v>91909</v>
+        <v>91910</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 15925-2026 artfynd.xlsx
+++ b/artfynd/A 15925-2026 artfynd.xlsx
@@ -913,7 +913,7 @@
         <v>132827217</v>
       </c>
       <c r="B4" t="n">
-        <v>91910</v>
+        <v>91912</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>132830899</v>
       </c>
       <c r="B5" t="n">
-        <v>101327</v>
+        <v>101329</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>132827269</v>
       </c>
       <c r="B6" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>132830905</v>
       </c>
       <c r="B7" t="n">
-        <v>101327</v>
+        <v>101329</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1452,57 +1452,52 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132830909</v>
+        <v>132830900</v>
       </c>
       <c r="B9" t="n">
-        <v>57951</v>
+        <v>101329</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skarnbro, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>696293</v>
+        <v>696261</v>
       </c>
       <c r="R9" t="n">
-        <v>6643676</v>
+        <v>6643641</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1534,7 +1529,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1539,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,45 +1566,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132830900</v>
+        <v>132830909</v>
       </c>
       <c r="B10" t="n">
-        <v>101327</v>
+        <v>57951</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skarnbro, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>696261</v>
+        <v>696293</v>
       </c>
       <c r="R10" t="n">
-        <v>6643641</v>
+        <v>6643676</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1681,7 +1681,7 @@
         <v>132827302</v>
       </c>
       <c r="B11" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,45 +1794,54 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132830907</v>
+        <v>132830903</v>
       </c>
       <c r="B12" t="n">
-        <v>91910</v>
+        <v>99121</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skarnbro, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>696302</v>
+        <v>696214</v>
       </c>
       <c r="R12" t="n">
-        <v>6643711</v>
+        <v>6643713</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1864,7 +1873,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1874,7 +1883,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1901,54 +1910,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132830903</v>
+        <v>132830907</v>
       </c>
       <c r="B13" t="n">
-        <v>99119</v>
+        <v>91912</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skarnbro, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>696214</v>
+        <v>696302</v>
       </c>
       <c r="R13" t="n">
-        <v>6643713</v>
+        <v>6643711</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2020,7 +2020,7 @@
         <v>132830908</v>
       </c>
       <c r="B14" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>132830904</v>
       </c>
       <c r="B15" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>132827400</v>
       </c>
       <c r="B16" t="n">
-        <v>91910</v>
+        <v>91912</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 15925-2026 artfynd.xlsx
+++ b/artfynd/A 15925-2026 artfynd.xlsx
@@ -910,45 +910,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132827217</v>
+        <v>132830899</v>
       </c>
       <c r="B4" t="n">
-        <v>91912</v>
+        <v>101330</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Skarnbro, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>696300</v>
+        <v>696275</v>
       </c>
       <c r="R4" t="n">
-        <v>6643713</v>
+        <v>6643599</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,57 +1005,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132830899</v>
+        <v>132827217</v>
       </c>
       <c r="B5" t="n">
-        <v>101329</v>
+        <v>91913</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skarnbro, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>696275</v>
+        <v>696300</v>
       </c>
       <c r="R5" t="n">
-        <v>6643599</v>
+        <v>6643713</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,12 +1112,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1127,7 +1127,7 @@
         <v>132827269</v>
       </c>
       <c r="B6" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>132830905</v>
       </c>
       <c r="B7" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>132830900</v>
       </c>
       <c r="B9" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>132827302</v>
       </c>
       <c r="B11" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
         <v>132830903</v>
       </c>
       <c r="B12" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>132830907</v>
       </c>
       <c r="B13" t="n">
-        <v>91912</v>
+        <v>91913</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>132830908</v>
       </c>
       <c r="B14" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>132830904</v>
       </c>
       <c r="B15" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>132827400</v>
       </c>
       <c r="B16" t="n">
-        <v>91912</v>
+        <v>91913</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 15925-2026 artfynd.xlsx
+++ b/artfynd/A 15925-2026 artfynd.xlsx
@@ -1459,45 +1459,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132830900</v>
+        <v>132830909</v>
       </c>
       <c r="B9" t="n">
-        <v>101330</v>
+        <v>57951</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skarnbro, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>696261</v>
+        <v>696293</v>
       </c>
       <c r="R9" t="n">
-        <v>6643641</v>
+        <v>6643676</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1539,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1566,50 +1571,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132830909</v>
+        <v>132830900</v>
       </c>
       <c r="B10" t="n">
-        <v>57951</v>
+        <v>101330</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skarnbro, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>696293</v>
+        <v>696261</v>
       </c>
       <c r="R10" t="n">
-        <v>6643676</v>
+        <v>6643641</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1794,54 +1794,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132830903</v>
+        <v>132830907</v>
       </c>
       <c r="B12" t="n">
-        <v>99122</v>
+        <v>91913</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skarnbro, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>696214</v>
+        <v>696302</v>
       </c>
       <c r="R12" t="n">
-        <v>6643713</v>
+        <v>6643711</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1873,7 +1864,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1883,7 +1874,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1910,45 +1901,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132830907</v>
+        <v>132830903</v>
       </c>
       <c r="B13" t="n">
-        <v>91913</v>
+        <v>99122</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skarnbro, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>696302</v>
+        <v>696214</v>
       </c>
       <c r="R13" t="n">
-        <v>6643711</v>
+        <v>6643713</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 15925-2026 artfynd.xlsx
+++ b/artfynd/A 15925-2026 artfynd.xlsx
@@ -910,45 +910,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132830899</v>
+        <v>132827217</v>
       </c>
       <c r="B4" t="n">
-        <v>101330</v>
+        <v>91913</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skarnbro, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>696275</v>
+        <v>696300</v>
       </c>
       <c r="R4" t="n">
-        <v>6643599</v>
+        <v>6643713</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,57 +1005,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132827217</v>
+        <v>132830899</v>
       </c>
       <c r="B5" t="n">
-        <v>91913</v>
+        <v>101330</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Skarnbro, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>696300</v>
+        <v>696275</v>
       </c>
       <c r="R5" t="n">
-        <v>6643713</v>
+        <v>6643599</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,12 +1112,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 15925-2026 artfynd.xlsx
+++ b/artfynd/A 15925-2026 artfynd.xlsx
@@ -1459,50 +1459,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132830909</v>
+        <v>132830900</v>
       </c>
       <c r="B9" t="n">
-        <v>57951</v>
+        <v>101330</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skarnbro, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>696293</v>
+        <v>696261</v>
       </c>
       <c r="R9" t="n">
-        <v>6643676</v>
+        <v>6643641</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1534,7 +1529,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1539,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,45 +1566,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132830900</v>
+        <v>132830909</v>
       </c>
       <c r="B10" t="n">
-        <v>101330</v>
+        <v>57951</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skarnbro, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>696261</v>
+        <v>696293</v>
       </c>
       <c r="R10" t="n">
-        <v>6643641</v>
+        <v>6643676</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 15925-2026 artfynd.xlsx
+++ b/artfynd/A 15925-2026 artfynd.xlsx
@@ -1794,45 +1794,54 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132830907</v>
+        <v>132830903</v>
       </c>
       <c r="B12" t="n">
-        <v>91913</v>
+        <v>99122</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skarnbro, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>696302</v>
+        <v>696214</v>
       </c>
       <c r="R12" t="n">
-        <v>6643711</v>
+        <v>6643713</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1864,7 +1873,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1874,7 +1883,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1901,54 +1910,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132830903</v>
+        <v>132830907</v>
       </c>
       <c r="B13" t="n">
-        <v>99122</v>
+        <v>91913</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skarnbro, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>696214</v>
+        <v>696302</v>
       </c>
       <c r="R13" t="n">
-        <v>6643713</v>
+        <v>6643711</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 15925-2026 artfynd.xlsx
+++ b/artfynd/A 15925-2026 artfynd.xlsx
@@ -1452,52 +1452,57 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132830900</v>
+        <v>132830909</v>
       </c>
       <c r="B9" t="n">
-        <v>101330</v>
+        <v>57951</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skarnbro, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>696261</v>
+        <v>696293</v>
       </c>
       <c r="R9" t="n">
-        <v>6643641</v>
+        <v>6643676</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1539,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1566,50 +1571,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132830909</v>
+        <v>132830900</v>
       </c>
       <c r="B10" t="n">
-        <v>57951</v>
+        <v>101330</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skarnbro, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>696293</v>
+        <v>696261</v>
       </c>
       <c r="R10" t="n">
-        <v>6643676</v>
+        <v>6643641</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1794,54 +1794,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132830903</v>
+        <v>132830907</v>
       </c>
       <c r="B12" t="n">
-        <v>99122</v>
+        <v>91913</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skarnbro, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>696214</v>
+        <v>696302</v>
       </c>
       <c r="R12" t="n">
-        <v>6643713</v>
+        <v>6643711</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1873,7 +1864,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1883,7 +1874,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1910,45 +1901,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132830907</v>
+        <v>132830903</v>
       </c>
       <c r="B13" t="n">
-        <v>91913</v>
+        <v>99122</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skarnbro, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>696302</v>
+        <v>696214</v>
       </c>
       <c r="R13" t="n">
-        <v>6643711</v>
+        <v>6643713</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2017,7 +2017,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132830908</v>
+        <v>132830904</v>
       </c>
       <c r="B14" t="n">
         <v>99122</v>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>696294</v>
+        <v>696201</v>
       </c>
       <c r="R14" t="n">
-        <v>6643676</v>
+        <v>6643715</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2133,7 +2133,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132830904</v>
+        <v>132830908</v>
       </c>
       <c r="B15" t="n">
         <v>99122</v>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2177,10 +2177,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>696201</v>
+        <v>696294</v>
       </c>
       <c r="R15" t="n">
-        <v>6643715</v>
+        <v>6643676</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 15925-2026 artfynd.xlsx
+++ b/artfynd/A 15925-2026 artfynd.xlsx
@@ -910,45 +910,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132827217</v>
+        <v>132830899</v>
       </c>
       <c r="B4" t="n">
-        <v>91913</v>
+        <v>101330</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Skarnbro, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>696300</v>
+        <v>696275</v>
       </c>
       <c r="R4" t="n">
-        <v>6643713</v>
+        <v>6643599</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,57 +1005,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132830899</v>
+        <v>132827217</v>
       </c>
       <c r="B5" t="n">
-        <v>101330</v>
+        <v>91913</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skarnbro, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>696275</v>
+        <v>696300</v>
       </c>
       <c r="R5" t="n">
-        <v>6643599</v>
+        <v>6643713</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,12 +1112,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -2017,7 +2017,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132830904</v>
+        <v>132830908</v>
       </c>
       <c r="B14" t="n">
         <v>99122</v>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>696201</v>
+        <v>696294</v>
       </c>
       <c r="R14" t="n">
-        <v>6643715</v>
+        <v>6643676</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2133,7 +2133,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132830908</v>
+        <v>132830904</v>
       </c>
       <c r="B15" t="n">
         <v>99122</v>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2177,10 +2177,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>696294</v>
+        <v>696201</v>
       </c>
       <c r="R15" t="n">
-        <v>6643676</v>
+        <v>6643715</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 15925-2026 artfynd.xlsx
+++ b/artfynd/A 15925-2026 artfynd.xlsx
@@ -910,45 +910,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132830899</v>
+        <v>132827217</v>
       </c>
       <c r="B4" t="n">
-        <v>101330</v>
+        <v>91916</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skarnbro, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>696275</v>
+        <v>696300</v>
       </c>
       <c r="R4" t="n">
-        <v>6643599</v>
+        <v>6643713</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,57 +1005,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132827217</v>
+        <v>132830899</v>
       </c>
       <c r="B5" t="n">
-        <v>91913</v>
+        <v>101333</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Skarnbro, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>696300</v>
+        <v>696275</v>
       </c>
       <c r="R5" t="n">
-        <v>6643713</v>
+        <v>6643599</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,12 +1112,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1127,7 +1127,7 @@
         <v>132827269</v>
       </c>
       <c r="B6" t="n">
-        <v>99122</v>
+        <v>99125</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>132830905</v>
       </c>
       <c r="B7" t="n">
-        <v>101330</v>
+        <v>101333</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>132827060</v>
       </c>
       <c r="B8" t="n">
-        <v>57951</v>
+        <v>57954</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>132830900</v>
       </c>
       <c r="B9" t="n">
-        <v>101330</v>
+        <v>101333</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>132830909</v>
       </c>
       <c r="B10" t="n">
-        <v>57951</v>
+        <v>57954</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>132827302</v>
       </c>
       <c r="B11" t="n">
-        <v>99122</v>
+        <v>99125</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
         <v>132830907</v>
       </c>
       <c r="B12" t="n">
-        <v>91913</v>
+        <v>91916</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>132830903</v>
       </c>
       <c r="B13" t="n">
-        <v>99122</v>
+        <v>99125</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>132830908</v>
       </c>
       <c r="B14" t="n">
-        <v>99122</v>
+        <v>99125</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>132830904</v>
       </c>
       <c r="B15" t="n">
-        <v>99122</v>
+        <v>99125</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>132827400</v>
       </c>
       <c r="B16" t="n">
-        <v>91913</v>
+        <v>91916</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>

--- a/artfynd/A 15925-2026 artfynd.xlsx
+++ b/artfynd/A 15925-2026 artfynd.xlsx
@@ -1459,45 +1459,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132830900</v>
+        <v>132830909</v>
       </c>
       <c r="B9" t="n">
-        <v>101333</v>
+        <v>57954</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skarnbro, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>696261</v>
+        <v>696293</v>
       </c>
       <c r="R9" t="n">
-        <v>6643641</v>
+        <v>6643676</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1539,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1566,50 +1571,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132830909</v>
+        <v>132830900</v>
       </c>
       <c r="B10" t="n">
-        <v>57954</v>
+        <v>101333</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skarnbro, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>696293</v>
+        <v>696261</v>
       </c>
       <c r="R10" t="n">
-        <v>6643676</v>
+        <v>6643641</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1794,45 +1794,54 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132830907</v>
+        <v>132830903</v>
       </c>
       <c r="B12" t="n">
-        <v>91916</v>
+        <v>99125</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skarnbro, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>696302</v>
+        <v>696214</v>
       </c>
       <c r="R12" t="n">
-        <v>6643711</v>
+        <v>6643713</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1864,7 +1873,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1874,7 +1883,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1901,54 +1910,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132830903</v>
+        <v>132830907</v>
       </c>
       <c r="B13" t="n">
-        <v>99125</v>
+        <v>91916</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skarnbro, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>696214</v>
+        <v>696302</v>
       </c>
       <c r="R13" t="n">
-        <v>6643713</v>
+        <v>6643711</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>

--- a/artfynd/A 15925-2026 artfynd.xlsx
+++ b/artfynd/A 15925-2026 artfynd.xlsx
@@ -913,7 +913,7 @@
         <v>132827217</v>
       </c>
       <c r="B4" t="n">
-        <v>91916</v>
+        <v>91917</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>132830899</v>
       </c>
       <c r="B5" t="n">
-        <v>101333</v>
+        <v>101334</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>132827269</v>
       </c>
       <c r="B6" t="n">
-        <v>99125</v>
+        <v>99126</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>132830905</v>
       </c>
       <c r="B7" t="n">
-        <v>101333</v>
+        <v>101334</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>132830900</v>
       </c>
       <c r="B10" t="n">
-        <v>101333</v>
+        <v>101334</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>132827302</v>
       </c>
       <c r="B11" t="n">
-        <v>99125</v>
+        <v>99126</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,54 +1794,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132830903</v>
+        <v>132830907</v>
       </c>
       <c r="B12" t="n">
-        <v>99125</v>
+        <v>91917</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skarnbro, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>696214</v>
+        <v>696302</v>
       </c>
       <c r="R12" t="n">
-        <v>6643713</v>
+        <v>6643711</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1873,7 +1864,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1883,7 +1874,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1910,45 +1901,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132830907</v>
+        <v>132830903</v>
       </c>
       <c r="B13" t="n">
-        <v>91916</v>
+        <v>99126</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skarnbro, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>696302</v>
+        <v>696214</v>
       </c>
       <c r="R13" t="n">
-        <v>6643711</v>
+        <v>6643713</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2020,7 +2020,7 @@
         <v>132830908</v>
       </c>
       <c r="B14" t="n">
-        <v>99125</v>
+        <v>99126</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>132830904</v>
       </c>
       <c r="B15" t="n">
-        <v>99125</v>
+        <v>99126</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>132827400</v>
       </c>
       <c r="B16" t="n">
-        <v>91916</v>
+        <v>91917</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 15925-2026 artfynd.xlsx
+++ b/artfynd/A 15925-2026 artfynd.xlsx
@@ -913,7 +913,7 @@
         <v>132827217</v>
       </c>
       <c r="B4" t="n">
-        <v>91917</v>
+        <v>91918</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>132830899</v>
       </c>
       <c r="B5" t="n">
-        <v>101334</v>
+        <v>101338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>132827269</v>
       </c>
       <c r="B6" t="n">
-        <v>99126</v>
+        <v>99130</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>132830905</v>
       </c>
       <c r="B7" t="n">
-        <v>101334</v>
+        <v>101338</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>132827060</v>
       </c>
       <c r="B8" t="n">
-        <v>57954</v>
+        <v>57955</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>132830909</v>
       </c>
       <c r="B9" t="n">
-        <v>57954</v>
+        <v>57955</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>132830900</v>
       </c>
       <c r="B10" t="n">
-        <v>101334</v>
+        <v>101338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>132827302</v>
       </c>
       <c r="B11" t="n">
-        <v>99126</v>
+        <v>99130</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,45 +1794,54 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132830907</v>
+        <v>132830903</v>
       </c>
       <c r="B12" t="n">
-        <v>91917</v>
+        <v>99130</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skarnbro, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>696302</v>
+        <v>696214</v>
       </c>
       <c r="R12" t="n">
-        <v>6643711</v>
+        <v>6643713</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1864,7 +1873,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1874,7 +1883,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1901,54 +1910,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132830903</v>
+        <v>132830907</v>
       </c>
       <c r="B13" t="n">
-        <v>99126</v>
+        <v>91918</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skarnbro, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>696214</v>
+        <v>696302</v>
       </c>
       <c r="R13" t="n">
-        <v>6643713</v>
+        <v>6643711</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2020,7 +2020,7 @@
         <v>132830908</v>
       </c>
       <c r="B14" t="n">
-        <v>99126</v>
+        <v>99130</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>132830904</v>
       </c>
       <c r="B15" t="n">
-        <v>99126</v>
+        <v>99130</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>132827400</v>
       </c>
       <c r="B16" t="n">
-        <v>91917</v>
+        <v>91918</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 15925-2026 artfynd.xlsx
+++ b/artfynd/A 15925-2026 artfynd.xlsx
@@ -1459,50 +1459,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132830909</v>
+        <v>132830900</v>
       </c>
       <c r="B9" t="n">
-        <v>57955</v>
+        <v>101338</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skarnbro, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>696293</v>
+        <v>696261</v>
       </c>
       <c r="R9" t="n">
-        <v>6643676</v>
+        <v>6643641</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1534,7 +1529,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1539,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,45 +1566,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132830900</v>
+        <v>132830909</v>
       </c>
       <c r="B10" t="n">
-        <v>101338</v>
+        <v>57955</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skarnbro, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>696261</v>
+        <v>696293</v>
       </c>
       <c r="R10" t="n">
-        <v>6643641</v>
+        <v>6643676</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1794,54 +1794,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132830903</v>
+        <v>132830907</v>
       </c>
       <c r="B12" t="n">
-        <v>99130</v>
+        <v>91918</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skarnbro, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>696214</v>
+        <v>696302</v>
       </c>
       <c r="R12" t="n">
-        <v>6643713</v>
+        <v>6643711</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1873,7 +1864,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1883,7 +1874,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1910,45 +1901,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132830907</v>
+        <v>132830903</v>
       </c>
       <c r="B13" t="n">
-        <v>91918</v>
+        <v>99130</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skarnbro, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>696302</v>
+        <v>696214</v>
       </c>
       <c r="R13" t="n">
-        <v>6643711</v>
+        <v>6643713</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 15925-2026 artfynd.xlsx
+++ b/artfynd/A 15925-2026 artfynd.xlsx
@@ -1459,45 +1459,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132830900</v>
+        <v>132830909</v>
       </c>
       <c r="B9" t="n">
-        <v>101338</v>
+        <v>57955</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skarnbro, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>696261</v>
+        <v>696293</v>
       </c>
       <c r="R9" t="n">
-        <v>6643641</v>
+        <v>6643676</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1539,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1566,50 +1571,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132830909</v>
+        <v>132830900</v>
       </c>
       <c r="B10" t="n">
-        <v>57955</v>
+        <v>101338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skarnbro, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>696293</v>
+        <v>696261</v>
       </c>
       <c r="R10" t="n">
-        <v>6643676</v>
+        <v>6643641</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 15925-2026 artfynd.xlsx
+++ b/artfynd/A 15925-2026 artfynd.xlsx
@@ -2017,7 +2017,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132830908</v>
+        <v>132830904</v>
       </c>
       <c r="B14" t="n">
         <v>99130</v>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>696294</v>
+        <v>696201</v>
       </c>
       <c r="R14" t="n">
-        <v>6643676</v>
+        <v>6643715</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2133,7 +2133,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132830904</v>
+        <v>132830908</v>
       </c>
       <c r="B15" t="n">
         <v>99130</v>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2177,10 +2177,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>696201</v>
+        <v>696294</v>
       </c>
       <c r="R15" t="n">
-        <v>6643715</v>
+        <v>6643676</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 15925-2026 artfynd.xlsx
+++ b/artfynd/A 15925-2026 artfynd.xlsx
@@ -2017,7 +2017,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132830904</v>
+        <v>132830908</v>
       </c>
       <c r="B14" t="n">
         <v>99130</v>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>696201</v>
+        <v>696294</v>
       </c>
       <c r="R14" t="n">
-        <v>6643715</v>
+        <v>6643676</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2133,7 +2133,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132830908</v>
+        <v>132830904</v>
       </c>
       <c r="B15" t="n">
         <v>99130</v>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2177,10 +2177,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>696294</v>
+        <v>696201</v>
       </c>
       <c r="R15" t="n">
-        <v>6643676</v>
+        <v>6643715</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 15925-2026 artfynd.xlsx
+++ b/artfynd/A 15925-2026 artfynd.xlsx
@@ -910,45 +910,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132827217</v>
+        <v>132830899</v>
       </c>
       <c r="B4" t="n">
-        <v>91918</v>
+        <v>101340</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Skarnbro, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>696300</v>
+        <v>696275</v>
       </c>
       <c r="R4" t="n">
-        <v>6643713</v>
+        <v>6643599</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,57 +1005,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132830899</v>
+        <v>132827217</v>
       </c>
       <c r="B5" t="n">
-        <v>101338</v>
+        <v>91920</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skarnbro, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>696275</v>
+        <v>696300</v>
       </c>
       <c r="R5" t="n">
-        <v>6643599</v>
+        <v>6643713</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,12 +1112,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1127,7 +1127,7 @@
         <v>132827269</v>
       </c>
       <c r="B6" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>132830905</v>
       </c>
       <c r="B7" t="n">
-        <v>101338</v>
+        <v>101340</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>132830900</v>
       </c>
       <c r="B10" t="n">
-        <v>101338</v>
+        <v>101340</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>132827302</v>
       </c>
       <c r="B11" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,45 +1794,54 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132830907</v>
+        <v>132830903</v>
       </c>
       <c r="B12" t="n">
-        <v>91918</v>
+        <v>99132</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skarnbro, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>696302</v>
+        <v>696214</v>
       </c>
       <c r="R12" t="n">
-        <v>6643711</v>
+        <v>6643713</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1864,7 +1873,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1874,7 +1883,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1901,54 +1910,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132830903</v>
+        <v>132830907</v>
       </c>
       <c r="B13" t="n">
-        <v>99130</v>
+        <v>91920</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skarnbro, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>696214</v>
+        <v>696302</v>
       </c>
       <c r="R13" t="n">
-        <v>6643713</v>
+        <v>6643711</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2020,7 +2020,7 @@
         <v>132830908</v>
       </c>
       <c r="B14" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>132830904</v>
       </c>
       <c r="B15" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>132827400</v>
       </c>
       <c r="B16" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 15925-2026 artfynd.xlsx
+++ b/artfynd/A 15925-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,56 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>55545406</v>
+        <v>132827217</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91974</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Eklund, NV om, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>696276.061761613</v>
+        <v>696300</v>
       </c>
       <c r="R2" t="n">
-        <v>6643760.129205355</v>
+        <v>6643713</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-10-07</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-10-07</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,67 +770,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>55545404</v>
+        <v>132827400</v>
       </c>
       <c r="B3" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91974</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Eklund, NV om, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>696296.9084280056</v>
+        <v>696298</v>
       </c>
       <c r="R3" t="n">
-        <v>6643632.994371749</v>
+        <v>6643648</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,27 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2015-10-07</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2015-10-07</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Gammal barrblandskog.</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,51 +871,50 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132830899</v>
+        <v>132830907</v>
       </c>
       <c r="B4" t="n">
-        <v>101340</v>
+        <v>91974</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -945,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>696275</v>
+        <v>696302</v>
       </c>
       <c r="R4" t="n">
-        <v>6643599</v>
+        <v>6643711</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -990,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,48 +996,58 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132827217</v>
+        <v>55545401</v>
       </c>
       <c r="B5" t="n">
-        <v>91920</v>
+        <v>91330</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>4189</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Pers., nom.sanct</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, NV om, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>696300</v>
+        <v>696313</v>
       </c>
       <c r="R5" t="n">
-        <v>6643713</v>
+        <v>6643640</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1082,22 +1071,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:41</t>
+          <t>2015-10-07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:41</t>
+          <t>2015-10-07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>I barrmatta under gammal gran. Gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,75 +1090,69 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132827269</v>
+        <v>55545402</v>
       </c>
       <c r="B6" t="n">
-        <v>99132</v>
+        <v>92869</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, NV om, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>696289</v>
+        <v>696313</v>
       </c>
       <c r="R6" t="n">
-        <v>6643668</v>
+        <v>6643640</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,22 +1176,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:47</t>
+          <t>2015-10-07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:47</t>
+          <t>2015-10-07</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1222,66 +1195,69 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132830905</v>
+        <v>55545404</v>
       </c>
       <c r="B7" t="n">
-        <v>101340</v>
+        <v>93233</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ramaren, Upl</t>
+          <t>Eklund, NV om, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
         <v>696297</v>
       </c>
       <c r="R7" t="n">
-        <v>6643754</v>
+        <v>6643633</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,22 +1281,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:28</t>
+          <t>2015-10-07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:28</t>
+          <t>2015-10-07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1329,18 +1300,19 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1350,11 +1322,11 @@
         <v>132827060</v>
       </c>
       <c r="B8" t="n">
-        <v>57955</v>
+        <v>57972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1462,11 +1434,11 @@
         <v>132830909</v>
       </c>
       <c r="B9" t="n">
-        <v>57955</v>
+        <v>57972</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1571,10 +1543,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132830900</v>
+        <v>132830902</v>
       </c>
       <c r="B10" t="n">
-        <v>101340</v>
+        <v>58131</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,34 +1554,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>103023</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skarnbro, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>696261</v>
+        <v>696274</v>
       </c>
       <c r="R10" t="n">
-        <v>6643641</v>
+        <v>6643661</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1621,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,7 +1631,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1678,57 +1658,51 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132827302</v>
+        <v>55545407</v>
       </c>
       <c r="B11" t="n">
-        <v>99132</v>
+        <v>111390</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>219711</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, NV om, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>696294</v>
+        <v>696326</v>
       </c>
       <c r="R11" t="n">
-        <v>6643666</v>
+        <v>6643740</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1752,22 +1726,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12:49</t>
+          <t>2015-10-07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>12:49</t>
+          <t>2015-10-07</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1782,22 +1751,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132830903</v>
+        <v>132827269</v>
       </c>
       <c r="B12" t="n">
-        <v>99132</v>
+        <v>99195</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1824,7 +1793,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1834,14 +1803,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Skarnbro, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>696214</v>
+        <v>696289</v>
       </c>
       <c r="R12" t="n">
-        <v>6643713</v>
+        <v>6643668</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1873,7 +1842,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1883,7 +1852,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1898,57 +1867,66 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132830907</v>
+        <v>132827302</v>
       </c>
       <c r="B13" t="n">
-        <v>91920</v>
+        <v>99195</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skarnbro, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>696302</v>
+        <v>696294</v>
       </c>
       <c r="R13" t="n">
-        <v>6643711</v>
+        <v>6643666</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1980,7 +1958,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1990,7 +1968,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2005,22 +1983,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132830908</v>
+        <v>132830903</v>
       </c>
       <c r="B14" t="n">
-        <v>99132</v>
+        <v>99195</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2047,7 +2025,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2061,10 +2039,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>696294</v>
+        <v>696214</v>
       </c>
       <c r="R14" t="n">
-        <v>6643676</v>
+        <v>6643713</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2096,7 +2074,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2106,7 +2084,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2136,7 +2114,7 @@
         <v>132830904</v>
       </c>
       <c r="B15" t="n">
-        <v>99132</v>
+        <v>99195</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2249,45 +2227,54 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132827400</v>
+        <v>132830908</v>
       </c>
       <c r="B16" t="n">
-        <v>91920</v>
+        <v>99195</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Skarnbro, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>696298</v>
+        <v>696294</v>
       </c>
       <c r="R16" t="n">
-        <v>6643648</v>
+        <v>6643676</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2319,7 +2306,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2329,7 +2316,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2344,15 +2331,741 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>55545403</v>
+      </c>
+      <c r="B17" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Eklund, NV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>696313</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6643640</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2015-10-07</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2015-10-07</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Gammal barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>55545406</v>
+      </c>
+      <c r="B18" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Eklund, NV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>696276</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6643760</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2015-10-07</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2015-10-07</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>55545410</v>
+      </c>
+      <c r="B19" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Eklund, NV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>696326</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6643740</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2015-10-07</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2015-10-07</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>132830899</v>
+      </c>
+      <c r="B20" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Skarnbro, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>696275</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6643599</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>132830900</v>
+      </c>
+      <c r="B21" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Skarnbro, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>696261</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6643641</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>132830905</v>
+      </c>
+      <c r="B22" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Ramaren, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>696297</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6643754</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>55545408</v>
+      </c>
+      <c r="B23" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Eklund, NV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>696326</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6643740</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2015-10-07</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2015-10-07</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15925-2026 artfynd.xlsx
+++ b/artfynd/A 15925-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132827217</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132827400</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830907</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1106,6 +1126,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55545401</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1211,6 +1236,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55545402</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1316,6 +1346,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55545404</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1428,6 +1463,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132827060</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1540,6 +1580,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830909</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1655,6 +1700,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830902</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1760,6 +1810,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55545407</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1876,6 +1931,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132827269</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1992,6 +2052,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132827302</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2108,6 +2173,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830903</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2224,6 +2294,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830904</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2340,6 +2415,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830908</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2445,6 +2525,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55545403</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2545,6 +2630,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55545406</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2645,6 +2735,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55545410</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2752,6 +2847,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830899</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2859,6 +2959,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830900</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2966,6 +3071,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830905</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3066,8 +3176,37 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55545408</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>